--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-05).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-182</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 1.765.619,20</t>
-  </si>
-  <si>
-    <t>R$ 9.195,93
-R$ 9.318,98</t>
-  </si>
-  <si>
-    <t>(8.5%)
+186</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>R$ 1.794.243,07</t>
+  </si>
+  <si>
+    <t>R$ 9.154,30
+R$ 9.272,46</t>
+  </si>
+  <si>
+    <t>(8.4%)
 (7.3%)</t>
   </si>
   <si>
-    <t>95.8</t>
+    <t>95.4</t>
   </si>
   <si>
     <t>(13.0%)</t>
   </si>
   <si>
-    <t>49.7%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
+    <t>50.1%</t>
+  </si>
+  <si>
+    <t>7.6%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,34 +947,34 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>30.5</t>
-  </si>
-  <si>
-    <t>59.3%</t>
-  </si>
-  <si>
-    <t>17.7%</t>
+    <t>30.7</t>
+  </si>
+  <si>
+    <t>59.2%</t>
+  </si>
+  <si>
+    <t>18.1%</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>8.1</t>
-  </si>
-  <si>
-    <t>15.4</t>
-  </si>
-  <si>
-    <t>21.8</t>
-  </si>
-  <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>-R$ 63.544,88</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>21.9</t>
+  </si>
+  <si>
+    <t>59.8%</t>
+  </si>
+  <si>
+    <t>-R$ 64.446,98</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4424,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4460,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>11648.91</v>
+      </c>
+      <c r="P24" s="5">
+        <v>11648.91</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.038610503340804847</v>
+      </c>
+      <c r="R24" s="7">
+        <v>132</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.050359712230215847</v>
+      </c>
+      <c r="T24" s="6">
+        <v>1.6395373558556123</v>
+      </c>
+      <c r="U24" s="6">
+        <v>1.3000283374152604</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.015891315153091577</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0004853243779890136</v>
+      </c>
+      <c r="X24" s="8">
+        <v>39.787339423076929</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.32692307692307693</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>7.4815384615384621</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>15.422916346153848</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>29.572916346153843</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.17307692307692307</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-902.10000000000002</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5960,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5996,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>5356.8400000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>5356.8400000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.11125784744435441</v>
+      </c>
+      <c r="R36" s="7">
+        <v>65</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.084507042253521125</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.32024001090194965</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.01283676570515453</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.10045950597740458</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.056915177604707247</v>
+      </c>
+      <c r="X36" s="8">
+        <v>25.935714285714283</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.8791000000000002</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.0639448979591837</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>10.045237</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>16.998638775510205</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.83673469387755106</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7881,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7917,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>707.22000000000003</v>
+      </c>
+      <c r="P51" s="5">
+        <v>707.22000000000003</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.65107260563241298</v>
+      </c>
+      <c r="R51" s="7">
+        <v>8</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.57894736842105265</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.33125477220666838</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.026563162806481719</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.17303526483979523</v>
+      </c>
+      <c r="X51" s="8">
+        <v>29.350000000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.6916624999999996</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>7.6333000000000002</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>17.949998999999998</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>24.883299999999998</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12640,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12679,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12713,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10910.9</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10910.9</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.064338367709558919</v>
+      </c>
+      <c r="R89" s="7">
+        <v>97</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.16379310344827591</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.11642521698485003</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.1987852606109487</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.020935257403147313</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0082415291130887459</v>
+      </c>
+      <c r="X89" s="8">
+        <v>48.611999999999995</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.44</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>13.438605102040817</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>15.73333404255319</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>36.415666000000002</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.059999999999999998</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16755,7 +16895,7 @@
         <v>-318.60000000000002</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17017,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17410,7 +17550,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18587,7 +18727,7 @@
         <v>-204.5</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18718,7 +18858,7 @@
         <v>-525.5</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20905,7 +21045,7 @@
         <v>-3079.3699999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21032,7 +21172,7 @@
         <v>-51</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22189,7 +22329,7 @@
         <v>-1263.0599999999999</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24267,7 +24407,9 @@
       <c r="AB179" s="8">
         <v>2.6039000000000003</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.3829779999999996</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.347163829787233</v>
       </c>
@@ -28352,7 +28494,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
